--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Note.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Note.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alojamento dos Oficiais Reais de Palmia</t>
+          <t>Quartel dos Oficiais Reais de Palmia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Da meia-noite até o anoitecer, ele vigia.</t>
+          <t>Da meia-noite ao anoitecer, ele observa.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>↓ Irmã mais nova ↑ Outra mulher</t>
+          <t>↓Irmãzinha  ↑Outra mulher</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Coloque-os aqui.</t>
+          <t>Deixem aqui.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Descanse nas fontes termais para se aquecer de dentro para fora!</t>
+          <t>Faça um "Descanso" na água termal para se aquecer por dentro!</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
